--- a/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M04/third/CF_M04_req_eval.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M04/third/CF_M04_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.8158</v>
       </c>
       <c r="D13" t="n">
+        <v>0.8857</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9557</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>The system shall allow users to initiate a session using their email or phone number.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -773,10 +777,6 @@
 phone number</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -807,14 +807,11 @@
           <t>The menu shall be accessible from more than one screen via the user's profile image.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>R_21</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -828,14 +825,11 @@
           <t>The menu must be accessible from more than one screen.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>CF_M04_R25</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -866,10 +860,6 @@
           <t>The system shall display a Home screen with relevant business information.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -884,10 +874,6 @@
 of my business</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -918,10 +904,6 @@
           <t>The system shall allow users to view images and videos associated with a review.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -935,10 +917,6 @@
           <t xml:space="preserve"> I want to be able to see images and videos associated with a review</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -969,10 +947,6 @@
           <t>The system shall allow users to access the application menu from different screens.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>FR</t>
@@ -986,10 +960,6 @@
           <t>I want to be able to access the application menu from different screens</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1025,9 +995,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1051,8 +1018,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1083,14 +1048,11 @@
           <t>If Cintia is active, the system shall display a response suggestion automatically upon opening the response modal.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1104,14 +1066,11 @@
           <t>If Cintia is active, the system must display a response suggestion.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1142,14 +1101,11 @@
           <t>The system shall display images and videos associated with a review under the review text.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_17</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1163,14 +1119,11 @@
           <t>The system must display the images and videos associated with a review.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1201,14 +1154,11 @@
           <t>If the user lacks Cintia credits, the system shall notify them and provide a button to purchase more.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1223,14 +1173,11 @@
 buy them.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1261,14 +1208,11 @@
           <t>The system shall allow the user to enter an email address or phone number.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1282,14 +1226,11 @@
           <t>The system must allow entering an email address or a phone number.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1325,9 +1266,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1351,8 +1289,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1383,14 +1319,11 @@
           <t>Upon clicking an image or video, it shall be displayed in full screen.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>R_17</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1404,14 +1337,11 @@
           <t>When clicking an image or video, it must be displayed in full screen.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1442,14 +1372,11 @@
           <t>The system shall display loading and error states when necessary.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1463,14 +1390,11 @@
           <t>The system must display loading and error statuses when necessary.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1501,14 +1425,11 @@
           <t>Each widget shall load its data autonomously.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1522,14 +1443,11 @@
           <t>Each widget must load its data autonomously.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1560,14 +1478,11 @@
           <t>The system shall handle authentication errors and incorrect codes.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1581,14 +1496,11 @@
           <t>The system must handle authentication errors and incorrect codes.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1619,14 +1531,11 @@
           <t>Images shall be navigable via horizontal scroll.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_17</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1640,14 +1549,11 @@
           <t>The images must be navigable via horizontal scrolling.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1678,14 +1584,11 @@
           <t>Access to functionalities requires valid authentication and unauthorized access is not permitted.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_29</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1699,14 +1602,11 @@
           <t>Access to features requires valid authentication and is not allows unauthorized access.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M04_R35</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1737,14 +1637,11 @@
           <t>The system shall send an OTP code to the indicated address or number.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1758,14 +1655,11 @@
           <t>The system must send an OTP code to the indicated address or number.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1796,14 +1690,11 @@
           <t>The Home screen shall display several independent informative widgets.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1817,14 +1708,11 @@
           <t>The Home screen must display several independent informative widgets.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1855,14 +1743,11 @@
           <t>The system shall display the response progressively (typing effect).</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1876,14 +1761,11 @@
           <t>The system must display the response progressively (typing effect).</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1914,14 +1796,11 @@
           <t>The user shall be able to enter the received OTP code.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1935,14 +1814,11 @@
           <t>The user must be able to enter the received OTP code.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1973,14 +1849,11 @@
           <t>The user shall be able to edit or replace the suggested response.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1994,14 +1867,11 @@
           <t>The user must be able to edit or replace the suggested response.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2032,14 +1902,11 @@
           <t>If the code is correct, the user shall log in successfully.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2053,14 +1920,11 @@
           <t>If the code is correct, the user must log in successfully.</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2091,14 +1955,11 @@
           <t>The system shall detect if the user has the Cintia functionality activated.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2112,14 +1973,11 @@
           <t>The system must detect if the user has the Cintia functionality activated.</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2155,9 +2013,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2181,8 +2036,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2213,14 +2066,11 @@
           <t>The application is displayed and functions correctly on emulators and physical Android and iOS devices.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>R_25</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2234,14 +2084,11 @@
           <t>The application displays and works correctly on emulators and physical Android and iOS devices.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>CF_M04_R31</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2272,14 +2119,11 @@
           <t>Main calls to the backend return a response in a time perceived as acceptable by the user.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>R_27</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2293,14 +2137,11 @@
           <t>The main calls to the backend return a response in a time perceived as acceptable by the user.</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>CF_M04_R33</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2331,14 +2172,11 @@
           <t>Main functionalities can be used without errors after a first use; no external instructions are required to complete basic actions.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>R_23</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2352,14 +2190,11 @@
           <t>The main functionalities can be used without errors after a first use; no external instructions are required to complete basic actions.</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>CF_M04_R29</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2390,14 +2225,11 @@
           <t>The code follows a clear architecture and is reviewable via PRs without difficulty.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>R_31</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2411,14 +2243,11 @@
           <t>The code follows a clear architecture and is reviewable through PRs without difficulty.</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>CF_M04_R37</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2454,9 +2283,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2480,8 +2306,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2517,9 +2341,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2543,8 +2364,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
